--- a/templates/炫富生活/scripts.xlsx
+++ b/templates/炫富生活/scripts.xlsx
@@ -413,12 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,6 +435,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>voiceover</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
@@ -441,13 +447,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>POV: your life after forex|Stop trading time for money|This is real freedom</t>
+          <t>THEY LAUGHED AT MY $50 DEPOSIT|NOW IT'S HOTEL LOBBIES AND CITY LIGHTS|I DON'T EXPLAIN ANYMORE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lifestyle_01</t>
+          <t>This is what my life looks like now.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pure_luxury_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SILENT MOVES|EXPENSIVE VIEWS|PRIVATE LIFE, PUBLIC RESULTS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>luxury car interior pov night|five star hotel elevator mirror|black card payment closeup|business class airport lounge|rooftop skyline night lifestyle|watch closeup wrist in car|quiet luxury apartment morning|designer shopping bags walking|villa infinity pool morning|champagne toast closeup</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>I kept it quiet until it looked like this.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pure_luxury_02</t>
         </is>
       </c>
     </row>
